--- a/output/pdf_financials_xlsx/CAN.xlsx
+++ b/output/pdf_financials_xlsx/CAN.xlsx
@@ -1126,13 +1126,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.244398</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.099372</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.593352</v>
       </c>
     </row>
     <row r="35">
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.244398</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.099372</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.593352</v>
       </c>
     </row>
     <row r="37">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/CAN.xlsx
+++ b/output/pdf_financials_xlsx/CAN.xlsx
@@ -2445,7 +2445,7 @@
         <v>0</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0</v>
+        <v>-0.26684</v>
       </c>
     </row>
     <row r="115">
@@ -4977,7 +4977,11 @@
           <t>Acquisition of investment</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
